--- a/Catalog.xlsx
+++ b/Catalog.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ormoshev\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC93CDD-7FB3-464B-B053-1203BA65EC27}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C3966C-24D3-420D-9F82-AC47C3A41D46}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="93">
   <si>
     <t>Наименование</t>
   </si>
@@ -126,18 +126,6 @@
     <t>A1820</t>
   </si>
   <si>
-    <t>DDS232(6)</t>
-  </si>
-  <si>
-    <t>Электронные</t>
-  </si>
-  <si>
-    <t>DDS232(5)</t>
-  </si>
-  <si>
-    <t>DTS232</t>
-  </si>
-  <si>
     <t>S12U16</t>
   </si>
   <si>
@@ -150,12 +138,6 @@
     <t>0.25-5(100)</t>
   </si>
   <si>
-    <t>DDS38</t>
-  </si>
-  <si>
-    <t>10(50)</t>
-  </si>
-  <si>
     <t>HXE110</t>
   </si>
   <si>
@@ -304,9 +286,6 @@
   </si>
   <si>
     <t>ПСЧ-4ТМ CT/VT</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>EM</t>
@@ -399,7 +378,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -416,9 +395,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -739,7 +715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" customWidth="1"/>
@@ -768,25 +744,27 @@
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
+      <c r="A2" s="2">
+        <v>500</v>
+      </c>
       <c r="B2" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C2" s="4">
         <v>6</v>
@@ -795,13 +773,13 @@
         <v>7</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H2" s="5">
         <v>8</v>
@@ -810,13 +788,15 @@
         <v>18</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
+      <c r="A3" s="2">
+        <v>501</v>
+      </c>
       <c r="B3" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C3" s="4">
         <v>6</v>
@@ -825,13 +805,13 @@
         <v>13</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H3" s="5">
         <v>8</v>
@@ -840,13 +820,15 @@
         <v>18</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
+      <c r="A4" s="2">
+        <v>502</v>
+      </c>
       <c r="B4" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C4" s="4">
         <v>6</v>
@@ -855,13 +837,13 @@
         <v>13</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H4" s="5">
         <v>8</v>
@@ -870,13 +852,15 @@
         <v>18</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
+      <c r="A5" s="2">
+        <v>503</v>
+      </c>
       <c r="B5" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C5" s="4">
         <v>6</v>
@@ -885,13 +869,13 @@
         <v>13</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H5" s="5">
         <v>8</v>
@@ -900,11 +884,13 @@
         <v>18</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
+      <c r="A6" s="2">
+        <v>504</v>
+      </c>
       <c r="B6" s="3" t="s">
         <v>25</v>
       </c>
@@ -918,10 +904,10 @@
         <v>26</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H6" s="5">
         <v>8</v>
@@ -930,11 +916,13 @@
         <v>22</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
+      <c r="A7" s="2">
+        <v>505</v>
+      </c>
       <c r="B7" s="3" t="s">
         <v>27</v>
       </c>
@@ -948,10 +936,10 @@
         <v>8</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H7" s="5">
         <v>8</v>
@@ -960,11 +948,13 @@
         <v>22</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
+      <c r="A8" s="2">
+        <v>505</v>
+      </c>
       <c r="B8" s="3" t="s">
         <v>27</v>
       </c>
@@ -978,10 +968,10 @@
         <v>11</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H8" s="5">
         <v>8</v>
@@ -990,13 +980,15 @@
         <v>22</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
+      <c r="A9" s="2">
+        <v>507</v>
+      </c>
       <c r="B9" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C9" s="4">
         <v>6</v>
@@ -1008,10 +1000,10 @@
         <v>14</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H9" s="5">
         <v>8</v>
@@ -1020,13 +1012,15 @@
         <v>22</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
+      <c r="A10" s="2">
+        <v>508</v>
+      </c>
       <c r="B10" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C10" s="4">
         <v>6</v>
@@ -1038,10 +1032,10 @@
         <v>14</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H10" s="5">
         <v>8</v>
@@ -1050,11 +1044,13 @@
         <v>22</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
+      <c r="A11" s="2">
+        <v>509</v>
+      </c>
       <c r="B11" s="3" t="s">
         <v>28</v>
       </c>
@@ -1068,10 +1064,10 @@
         <v>8</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H11" s="5">
         <v>8</v>
@@ -1080,11 +1076,13 @@
         <v>14</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
+      <c r="A12" s="2">
+        <v>510</v>
+      </c>
       <c r="B12" s="3" t="s">
         <v>29</v>
       </c>
@@ -1098,10 +1096,10 @@
         <v>11</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H12" s="5">
         <v>8</v>
@@ -1110,13 +1108,15 @@
         <v>14</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2">
+        <v>511</v>
+      </c>
       <c r="B13" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C13" s="4">
         <v>6</v>
@@ -1128,10 +1128,10 @@
         <v>14</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H13" s="5">
         <v>8</v>
@@ -1140,13 +1140,15 @@
         <v>14</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2">
+        <v>512</v>
+      </c>
       <c r="B14" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C14" s="4">
         <v>6</v>
@@ -1158,10 +1160,10 @@
         <v>14</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H14" s="5">
         <v>8</v>
@@ -1170,13 +1172,15 @@
         <v>14</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
+      <c r="A15" s="2">
+        <v>513</v>
+      </c>
       <c r="B15" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C15" s="4">
         <v>6</v>
@@ -1188,10 +1192,10 @@
         <v>8</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H15" s="5">
         <v>8</v>
@@ -1200,13 +1204,15 @@
         <v>5</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
+      <c r="A16" s="2">
+        <v>514</v>
+      </c>
       <c r="B16" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C16" s="4">
         <v>6</v>
@@ -1218,10 +1224,10 @@
         <v>11</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H16" s="5">
         <v>8</v>
@@ -1230,13 +1236,15 @@
         <v>5</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
+      <c r="A17" s="2">
+        <v>515</v>
+      </c>
       <c r="B17" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C17" s="4">
         <v>6</v>
@@ -1248,10 +1256,10 @@
         <v>14</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H17" s="5">
         <v>8</v>
@@ -1260,13 +1268,15 @@
         <v>5</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
+      <c r="A18" s="2">
+        <v>516</v>
+      </c>
       <c r="B18" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C18" s="4">
         <v>6</v>
@@ -1278,10 +1288,10 @@
         <v>14</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H18" s="5">
         <v>8</v>
@@ -1290,11 +1300,13 @@
         <v>5</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
+      <c r="A19" s="2">
+        <v>517</v>
+      </c>
       <c r="B19" s="3" t="s">
         <v>22</v>
       </c>
@@ -1308,10 +1320,10 @@
         <v>8</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H19" s="5">
         <v>8</v>
@@ -1320,11 +1332,13 @@
         <v>26</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
+      <c r="A20" s="2">
+        <v>518</v>
+      </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
@@ -1338,10 +1352,10 @@
         <v>11</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H20" s="5">
         <v>8</v>
@@ -1350,11 +1364,13 @@
         <v>26</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
+      <c r="A21" s="2">
+        <v>519</v>
+      </c>
       <c r="B21" s="3" t="s">
         <v>23</v>
       </c>
@@ -1368,10 +1384,10 @@
         <v>14</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H21" s="5">
         <v>8</v>
@@ -1380,13 +1396,15 @@
         <v>26</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
+      <c r="A22" s="2">
+        <v>520</v>
+      </c>
       <c r="B22" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C22" s="4">
         <v>6</v>
@@ -1398,10 +1416,10 @@
         <v>8</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H22" s="5">
         <v>8</v>
@@ -1410,13 +1428,15 @@
         <v>26</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
+      <c r="A23" s="2">
+        <v>521</v>
+      </c>
       <c r="B23" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C23" s="4">
         <v>6</v>
@@ -1428,10 +1448,10 @@
         <v>11</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H23" s="5">
         <v>8</v>
@@ -1440,13 +1460,15 @@
         <v>26</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
+      <c r="A24" s="2">
+        <v>522</v>
+      </c>
       <c r="B24" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C24" s="4">
         <v>5</v>
@@ -1458,10 +1480,10 @@
         <v>14</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H24" s="5">
         <v>8</v>
@@ -1470,13 +1492,15 @@
         <v>26</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
+      <c r="A25" s="2">
+        <v>523</v>
+      </c>
       <c r="B25" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C25" s="4">
         <v>6</v>
@@ -1488,10 +1512,10 @@
         <v>8</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H25" s="5">
         <v>8</v>
@@ -1500,13 +1524,15 @@
         <v>25</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
+      <c r="A26" s="2">
+        <v>524</v>
+      </c>
       <c r="B26" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C26" s="4">
         <v>6</v>
@@ -1518,10 +1544,10 @@
         <v>11</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H26" s="5">
         <v>8</v>
@@ -1530,13 +1556,15 @@
         <v>25</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
+      <c r="A27" s="2">
+        <v>525</v>
+      </c>
       <c r="B27" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C27" s="4">
         <v>6</v>
@@ -1548,10 +1576,10 @@
         <v>14</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H27" s="5">
         <v>8</v>
@@ -1560,11 +1588,13 @@
         <v>25</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
+      <c r="A28" s="2">
+        <v>526</v>
+      </c>
       <c r="B28" s="3" t="s">
         <v>19</v>
       </c>
@@ -1578,10 +1608,10 @@
         <v>10</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H28" s="5">
         <v>8</v>
@@ -1590,11 +1620,13 @@
         <v>24</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
+      <c r="A29" s="2">
+        <v>527</v>
+      </c>
       <c r="B29" s="3" t="s">
         <v>20</v>
       </c>
@@ -1608,10 +1640,10 @@
         <v>11</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H29" s="5">
         <v>8</v>
@@ -1620,13 +1652,15 @@
         <v>24</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
+      <c r="A30" s="2">
+        <v>528</v>
+      </c>
       <c r="B30" s="3" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C30" s="4">
         <v>8</v>
@@ -1638,10 +1672,10 @@
         <v>21</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H30" s="5">
         <v>8</v>
@@ -1650,13 +1684,15 @@
         <v>24</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
+      <c r="A31" s="2">
+        <v>529</v>
+      </c>
       <c r="B31" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C31" s="4">
         <v>8</v>
@@ -1668,10 +1704,10 @@
         <v>21</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H31" s="5">
         <v>8</v>
@@ -1680,11 +1716,13 @@
         <v>24</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
+      <c r="A32" s="2">
+        <v>530</v>
+      </c>
       <c r="B32" s="3" t="s">
         <v>17</v>
       </c>
@@ -1698,19 +1736,25 @@
         <v>10</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H32" s="5">
         <v>8</v>
       </c>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
+      <c r="I32" s="5">
+        <v>8</v>
+      </c>
+      <c r="J32" s="5">
+        <v>8</v>
+      </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
+      <c r="A33" s="2">
+        <v>531</v>
+      </c>
       <c r="B33" s="3" t="s">
         <v>18</v>
       </c>
@@ -1724,21 +1768,27 @@
         <v>11</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H33" s="5">
         <v>8</v>
       </c>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
+      <c r="I33" s="5">
+        <v>8</v>
+      </c>
+      <c r="J33" s="5">
+        <v>8</v>
+      </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
+      <c r="A34" s="2">
+        <v>532</v>
+      </c>
       <c r="B34" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C34" s="4">
         <v>6</v>
@@ -1750,23 +1800,29 @@
         <v>14</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H34" s="5">
         <v>8</v>
       </c>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
+      <c r="I34" s="5">
+        <v>8</v>
+      </c>
+      <c r="J34" s="5">
+        <v>8</v>
+      </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="7"/>
+      <c r="A35" s="2">
+        <v>533</v>
+      </c>
       <c r="B35" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="7">
         <v>6</v>
       </c>
       <c r="D35" s="6" t="s">
@@ -1776,10 +1832,10 @@
         <v>8</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H35" s="5">
         <v>8</v>
@@ -1788,15 +1844,17 @@
         <v>23</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="7"/>
+      <c r="A36" s="2">
+        <v>534</v>
+      </c>
       <c r="B36" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="8">
+      <c r="C36" s="7">
         <v>6</v>
       </c>
       <c r="D36" s="6" t="s">
@@ -1806,10 +1864,10 @@
         <v>8</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H36" s="5">
         <v>8</v>
@@ -1818,15 +1876,17 @@
         <v>23</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="7"/>
+      <c r="A37" s="2">
+        <v>534</v>
+      </c>
       <c r="B37" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C37" s="8">
+      <c r="C37" s="7">
         <v>6</v>
       </c>
       <c r="D37" s="6" t="s">
@@ -1836,10 +1896,10 @@
         <v>11</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H37" s="5">
         <v>8</v>
@@ -1848,15 +1908,17 @@
         <v>23</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="7"/>
+      <c r="A38" s="2">
+        <v>536</v>
+      </c>
       <c r="B38" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C38" s="8">
+        <v>74</v>
+      </c>
+      <c r="C38" s="7">
         <v>5</v>
       </c>
       <c r="D38" s="6" t="s">
@@ -1865,11 +1927,11 @@
       <c r="E38" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F38" s="9" t="s">
-        <v>62</v>
+      <c r="F38" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H38" s="5">
         <v>8</v>
@@ -1878,15 +1940,17 @@
         <v>23</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="7"/>
+      <c r="A39" s="2">
+        <v>537</v>
+      </c>
       <c r="B39" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C39" s="8">
+        <v>75</v>
+      </c>
+      <c r="C39" s="7">
         <v>6</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -1895,11 +1959,11 @@
       <c r="E39" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F39" s="9" t="s">
-        <v>62</v>
+      <c r="F39" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H39" s="5">
         <v>8</v>
@@ -1908,15 +1972,17 @@
         <v>23</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="7"/>
+      <c r="A40" s="2">
+        <v>538</v>
+      </c>
       <c r="B40" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40" s="8">
+        <v>76</v>
+      </c>
+      <c r="C40" s="7">
         <v>6</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -1925,11 +1991,11 @@
       <c r="E40" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F40" s="9" t="s">
-        <v>62</v>
+      <c r="F40" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H40" s="5">
         <v>8</v>
@@ -1938,15 +2004,17 @@
         <v>23</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
+      <c r="A41" s="2">
+        <v>539</v>
+      </c>
       <c r="B41" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C41" s="8">
+        <v>77</v>
+      </c>
+      <c r="C41" s="7">
         <v>6</v>
       </c>
       <c r="D41" s="6" t="s">
@@ -1955,11 +2023,11 @@
       <c r="E41" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F41" s="9" t="s">
-        <v>62</v>
+      <c r="F41" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H41" s="5">
         <v>8</v>
@@ -1968,15 +2036,17 @@
         <v>23</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="7"/>
+      <c r="A42" s="2">
+        <v>540</v>
+      </c>
       <c r="B42" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C42" s="8">
+        <v>73</v>
+      </c>
+      <c r="C42" s="7">
         <v>5</v>
       </c>
       <c r="D42" s="6" t="s">
@@ -1985,11 +2055,11 @@
       <c r="E42" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F42" s="9" t="s">
-        <v>61</v>
+      <c r="F42" s="8" t="s">
+        <v>55</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H42" s="5">
         <v>8</v>
@@ -1998,15 +2068,17 @@
         <v>23</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="7"/>
+      <c r="A43" s="2">
+        <v>541</v>
+      </c>
       <c r="B43" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C43" s="8">
+      <c r="C43" s="7">
         <v>6</v>
       </c>
       <c r="D43" s="6" t="s">
@@ -2015,11 +2087,11 @@
       <c r="E43" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F43" s="9" t="s">
-        <v>62</v>
+      <c r="F43" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H43" s="5">
         <v>8</v>
@@ -2028,15 +2100,17 @@
         <v>23</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="7"/>
+      <c r="A44" s="2">
+        <v>542</v>
+      </c>
       <c r="B44" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C44" s="8">
+        <v>71</v>
+      </c>
+      <c r="C44" s="7">
         <v>6</v>
       </c>
       <c r="D44" s="6" t="s">
@@ -2045,11 +2119,11 @@
       <c r="E44" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F44" s="9" t="s">
-        <v>62</v>
+      <c r="F44" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H44" s="5">
         <v>8</v>
@@ -2058,15 +2132,17 @@
         <v>23</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="7"/>
+      <c r="A45" s="2">
+        <v>543</v>
+      </c>
       <c r="B45" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C45" s="8">
+        <v>68</v>
+      </c>
+      <c r="C45" s="7">
         <v>5</v>
       </c>
       <c r="D45" s="6" t="s">
@@ -2075,11 +2151,11 @@
       <c r="E45" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F45" s="9" t="s">
-        <v>62</v>
+      <c r="F45" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H45" s="5">
         <v>8</v>
@@ -2088,15 +2164,17 @@
         <v>23</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="7"/>
+      <c r="A46" s="2">
+        <v>544</v>
+      </c>
       <c r="B46" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C46" s="8">
+        <v>69</v>
+      </c>
+      <c r="C46" s="7">
         <v>6</v>
       </c>
       <c r="D46" s="6" t="s">
@@ -2105,11 +2183,11 @@
       <c r="E46" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F46" s="9" t="s">
-        <v>62</v>
+      <c r="F46" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H46" s="5">
         <v>8</v>
@@ -2118,15 +2196,17 @@
         <v>23</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="7"/>
+      <c r="A47" s="2">
+        <v>545</v>
+      </c>
       <c r="B47" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C47" s="8">
+        <v>67</v>
+      </c>
+      <c r="C47" s="7">
         <v>5</v>
       </c>
       <c r="D47" s="6" t="s">
@@ -2135,11 +2215,11 @@
       <c r="E47" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>61</v>
+      <c r="F47" s="8" t="s">
+        <v>55</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H47" s="5">
         <v>8</v>
@@ -2148,15 +2228,17 @@
         <v>23</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="7"/>
+      <c r="A48" s="2">
+        <v>546</v>
+      </c>
       <c r="B48" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C48" s="8">
+        <v>70</v>
+      </c>
+      <c r="C48" s="7">
         <v>6</v>
       </c>
       <c r="D48" s="6" t="s">
@@ -2165,11 +2247,11 @@
       <c r="E48" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F48" s="9" t="s">
-        <v>62</v>
+      <c r="F48" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H48" s="5">
         <v>8</v>
@@ -2178,15 +2260,17 @@
         <v>23</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="7"/>
+      <c r="A49" s="2">
+        <v>547</v>
+      </c>
       <c r="B49" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C49" s="8">
+        <v>72</v>
+      </c>
+      <c r="C49" s="7">
         <v>6</v>
       </c>
       <c r="D49" s="6" t="s">
@@ -2195,11 +2279,11 @@
       <c r="E49" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F49" s="9" t="s">
-        <v>62</v>
+      <c r="F49" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H49" s="5">
         <v>8</v>
@@ -2208,15 +2292,17 @@
         <v>23</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="7"/>
+      <c r="A50" s="2">
+        <v>548</v>
+      </c>
       <c r="B50" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C50" s="8">
+      <c r="C50" s="7">
         <v>5</v>
       </c>
       <c r="D50" s="6" t="s">
@@ -2225,11 +2311,11 @@
       <c r="E50" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F50" s="9" t="s">
-        <v>62</v>
+      <c r="F50" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H50" s="5">
         <v>8</v>
@@ -2238,15 +2324,17 @@
         <v>23</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="7"/>
+      <c r="A51" s="2">
+        <v>549</v>
+      </c>
       <c r="B51" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="8">
+      <c r="C51" s="7">
         <v>6</v>
       </c>
       <c r="D51" s="6" t="s">
@@ -2255,11 +2343,11 @@
       <c r="E51" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F51" s="9" t="s">
-        <v>62</v>
+      <c r="F51" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H51" s="5">
         <v>8</v>
@@ -2268,15 +2356,17 @@
         <v>23</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="7"/>
+      <c r="A52" s="2">
+        <v>550</v>
+      </c>
       <c r="B52" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C52" s="8">
+        <v>66</v>
+      </c>
+      <c r="C52" s="7">
         <v>5</v>
       </c>
       <c r="D52" s="6" t="s">
@@ -2285,11 +2375,11 @@
       <c r="E52" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F52" s="9" t="s">
-        <v>61</v>
+      <c r="F52" s="8" t="s">
+        <v>55</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H52" s="5">
         <v>8</v>
@@ -2298,15 +2388,17 @@
         <v>23</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="7"/>
+      <c r="A53" s="2">
+        <v>551</v>
+      </c>
       <c r="B53" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C53" s="8">
+        <v>83</v>
+      </c>
+      <c r="C53" s="7">
         <v>6</v>
       </c>
       <c r="D53" s="6" t="s">
@@ -2315,24 +2407,30 @@
       <c r="E53" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F53" s="9" t="s">
-        <v>61</v>
+      <c r="F53" s="8" t="s">
+        <v>55</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H53" s="5">
         <v>8</v>
       </c>
-      <c r="I53" s="5"/>
-      <c r="J53" s="5"/>
+      <c r="I53" s="5">
+        <v>8</v>
+      </c>
+      <c r="J53" s="5">
+        <v>8</v>
+      </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="7"/>
+      <c r="A54" s="2">
+        <v>552</v>
+      </c>
       <c r="B54" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C54" s="8">
+        <v>82</v>
+      </c>
+      <c r="C54" s="7">
         <v>6</v>
       </c>
       <c r="D54" s="6" t="s">
@@ -2341,24 +2439,30 @@
       <c r="E54" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F54" s="9" t="s">
-        <v>62</v>
+      <c r="F54" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H54" s="5">
         <v>8</v>
       </c>
-      <c r="I54" s="5"/>
-      <c r="J54" s="5"/>
+      <c r="I54" s="5">
+        <v>8</v>
+      </c>
+      <c r="J54" s="5">
+        <v>8</v>
+      </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="7"/>
+      <c r="A55" s="2">
+        <v>553</v>
+      </c>
       <c r="B55" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C55" s="8">
+        <v>86</v>
+      </c>
+      <c r="C55" s="7">
         <v>6</v>
       </c>
       <c r="D55" s="6" t="s">
@@ -2367,24 +2471,30 @@
       <c r="E55" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F55" s="9" t="s">
-        <v>61</v>
+      <c r="F55" s="8" t="s">
+        <v>55</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H55" s="5">
         <v>8</v>
       </c>
-      <c r="I55" s="5"/>
-      <c r="J55" s="5"/>
+      <c r="I55" s="5">
+        <v>8</v>
+      </c>
+      <c r="J55" s="5">
+        <v>8</v>
+      </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="7"/>
+      <c r="A56" s="2">
+        <v>554</v>
+      </c>
       <c r="B56" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C56" s="8">
+        <v>81</v>
+      </c>
+      <c r="C56" s="7">
         <v>6</v>
       </c>
       <c r="D56" s="6" t="s">
@@ -2393,102 +2503,126 @@
       <c r="E56" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F56" s="9" t="s">
-        <v>62</v>
+      <c r="F56" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H56" s="5">
         <v>8</v>
       </c>
-      <c r="I56" s="5"/>
-      <c r="J56" s="5"/>
+      <c r="I56" s="5">
+        <v>8</v>
+      </c>
+      <c r="J56" s="5">
+        <v>8</v>
+      </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="7"/>
+      <c r="A57" s="2">
+        <v>555</v>
+      </c>
       <c r="B57" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C57" s="8">
+        <v>78</v>
+      </c>
+      <c r="C57" s="7">
         <v>5</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>85</v>
+        <v>80</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H57" s="5">
         <v>8</v>
       </c>
-      <c r="I57" s="5"/>
-      <c r="J57" s="5"/>
+      <c r="I57" s="5">
+        <v>8</v>
+      </c>
+      <c r="J57" s="5">
+        <v>8</v>
+      </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="7"/>
+      <c r="A58" s="2">
+        <v>556</v>
+      </c>
       <c r="B58" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C58" s="8">
+      <c r="C58" s="7">
         <v>5</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>85</v>
+        <v>80</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H58" s="5">
         <v>8</v>
       </c>
-      <c r="I58" s="5"/>
-      <c r="J58" s="5"/>
+      <c r="I58" s="5">
+        <v>8</v>
+      </c>
+      <c r="J58" s="5">
+        <v>8</v>
+      </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="7"/>
+      <c r="A59" s="2">
+        <v>557</v>
+      </c>
       <c r="B59" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C59" s="8">
+      <c r="C59" s="7">
         <v>5</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>85</v>
+        <v>80</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H59" s="5">
         <v>8</v>
       </c>
-      <c r="I59" s="5"/>
-      <c r="J59" s="5"/>
+      <c r="I59" s="5">
+        <v>8</v>
+      </c>
+      <c r="J59" s="5">
+        <v>8</v>
+      </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="7"/>
+      <c r="A60" s="2">
+        <v>558</v>
+      </c>
       <c r="B60" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C60" s="8">
+      <c r="C60" s="7">
         <v>5</v>
       </c>
       <c r="D60" s="6" t="s">
@@ -2497,24 +2631,30 @@
       <c r="E60" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F60" s="9" t="s">
-        <v>85</v>
+      <c r="F60" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H60" s="5">
         <v>8</v>
       </c>
-      <c r="I60" s="5"/>
-      <c r="J60" s="5"/>
+      <c r="I60" s="5">
+        <v>8</v>
+      </c>
+      <c r="J60" s="5">
+        <v>8</v>
+      </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="7"/>
+      <c r="A61" s="2">
+        <v>559</v>
+      </c>
       <c r="B61" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C61" s="8">
+        <v>84</v>
+      </c>
+      <c r="C61" s="7">
         <v>6</v>
       </c>
       <c r="D61" s="6" t="s">
@@ -2523,24 +2663,30 @@
       <c r="E61" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F61" s="9" t="s">
-        <v>61</v>
+      <c r="F61" s="8" t="s">
+        <v>55</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H61" s="5">
         <v>8</v>
       </c>
-      <c r="I61" s="5"/>
-      <c r="J61" s="5"/>
+      <c r="I61" s="5">
+        <v>8</v>
+      </c>
+      <c r="J61" s="5">
+        <v>8</v>
+      </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="7"/>
+      <c r="A62" s="2">
+        <v>560</v>
+      </c>
       <c r="B62" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C62" s="8">
+        <v>85</v>
+      </c>
+      <c r="C62" s="7">
         <v>6</v>
       </c>
       <c r="D62" s="6" t="s">
@@ -2549,147 +2695,21 @@
       <c r="E62" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F62" s="9" t="s">
-        <v>62</v>
+      <c r="F62" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H62" s="5">
         <v>8</v>
       </c>
-      <c r="I62" s="5"/>
-      <c r="J62" s="5"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="7"/>
-      <c r="B63" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C63" s="8">
-        <v>6</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="G63" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H63" s="5">
-        <v>8</v>
-      </c>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="7"/>
-      <c r="B64" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C64" s="8">
-        <v>5</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H64" s="5">
-        <v>8</v>
-      </c>
-      <c r="I64" s="5"/>
-      <c r="J64" s="5"/>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="7"/>
-      <c r="B65" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C65" s="8">
-        <v>6</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G65" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H65" s="5">
-        <v>4</v>
-      </c>
-      <c r="I65" s="5"/>
-      <c r="J65" s="5"/>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="7"/>
-      <c r="B66" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C66" s="8">
-        <v>6</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E66" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F66" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G66" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H66" s="5">
-        <v>4</v>
-      </c>
-      <c r="I66" s="5"/>
-      <c r="J66" s="5"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="7"/>
-      <c r="B67" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C67" s="8">
-        <v>6</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F67" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="G67" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H67" s="5">
-        <v>8</v>
-      </c>
-      <c r="I67" s="5"/>
-      <c r="J67" s="5"/>
+      <c r="I62" s="5">
+        <v>8</v>
+      </c>
+      <c r="J62" s="5">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Catalog.xlsx
+++ b/Catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ormoshev\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C3966C-24D3-420D-9F82-AC47C3A41D46}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FD97B9-2CCB-46B6-8D82-6729C4AB04AA}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -953,7 +953,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>27</v>
@@ -1881,7 +1881,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>9</v>
